--- a/main/ig/StructureDefinition-dmi-device.xlsx
+++ b/main/ig/StructureDefinition-dmi-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-device.xlsx
+++ b/main/ig/StructureDefinition-dmi-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-device.xlsx
+++ b/main/ig/StructureDefinition-dmi-device.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="404">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Device.id</t>
@@ -307,10 +307,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Device.implicitRules</t>
   </si>
   <si>
@@ -330,6 +337,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Device.language</t>
   </si>
   <si>
@@ -407,26 +417,33 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Device.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -453,10 +470,6 @@
     <t>Extension créée dans ce volet pour représenter l'IP Id logiciel.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Device.extension:MarquageCE</t>
   </si>
   <si>
@@ -492,10 +505,6 @@
     <t>Device.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -503,9 +512,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -550,6 +556,16 @@
     <t>The reference to the definition for the device.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>Device.udiCarrier</t>
   </si>
   <si>
@@ -585,13 +601,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Device.udiCarrier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -628,6 +638,9 @@
   </si>
   <si>
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Role.id.extension</t>
@@ -660,6 +673,9 @@
 http://hl7.org/fhir/NamingSystem/iccbba-other-di.</t>
   </si>
   <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
+  </si>
+  <si>
     <t>Role.id.root</t>
   </si>
   <si>
@@ -792,6 +808,9 @@
     <t>Reason for the dtatus of the Device availability.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -799,6 +818,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>CD</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -1054,6 +1076,9 @@
     <t>A single component of the device version.</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Device.version.value</t>
   </si>
   <si>
@@ -1103,6 +1128,16 @@
     <t>Property value as a quantity.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+  </si>
+  <si>
     <t>Device.property.valueCode</t>
   </si>
   <si>
@@ -1169,6 +1204,10 @@
     <t>used for troubleshooting etc.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
+  </si>
+  <si>
     <t>.scopedRole[typeCode=CON].player</t>
   </si>
   <si>
@@ -1220,6 +1259,9 @@
   </si>
   <si>
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>.text</t>
@@ -1577,14 +1619,14 @@
     <col min="26" max="26" width="43.49609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="52.640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="230.36328125" customWidth="true" bestFit="true"/>
   </cols>
@@ -2022,13 +2064,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>76</v>
@@ -2039,10 +2081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2065,16 +2107,16 @@
         <v>85</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2124,7 +2166,7 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
@@ -2133,13 +2175,13 @@
         <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>76</v>
@@ -2150,10 +2192,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2176,16 +2218,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2211,13 +2253,13 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -2235,7 +2277,7 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -2244,13 +2286,13 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>76</v>
@@ -2261,14 +2303,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2287,16 +2329,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2346,7 +2388,7 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
@@ -2355,13 +2397,13 @@
         <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>76</v>
@@ -2372,14 +2414,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2398,16 +2440,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2457,7 +2499,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2472,7 +2514,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>76</v>
@@ -2483,14 +2525,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2509,15 +2551,17 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>76</v>
@@ -2554,17 +2598,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2573,13 +2619,13 @@
         <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>76</v>
@@ -2590,13 +2636,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -2618,13 +2664,13 @@
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2675,7 +2721,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2684,10 +2730,10 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2701,13 +2747,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>76</v>
@@ -2729,13 +2775,13 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2786,7 +2832,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2795,10 +2841,10 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>76</v>
@@ -2812,13 +2858,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>76</v>
@@ -2840,13 +2886,13 @@
         <v>76</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2897,7 +2943,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2906,10 +2952,10 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>76</v>
@@ -2923,14 +2969,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2949,19 +2995,19 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -2998,19 +3044,19 @@
         <v>76</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3019,13 +3065,13 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
@@ -3036,10 +3082,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3062,16 +3108,16 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3121,7 +3167,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3130,27 +3176,27 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3173,15 +3219,17 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3230,7 +3278,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3239,13 +3287,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -3256,10 +3304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3282,16 +3330,16 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3341,7 +3389,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3350,16 +3398,16 @@
         <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>76</v>
@@ -3367,10 +3415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3393,13 +3441,13 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3450,7 +3498,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3465,7 +3513,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3476,14 +3524,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3502,16 +3550,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3549,19 +3597,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3570,13 +3618,13 @@
         <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3587,14 +3635,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3613,19 +3661,19 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3674,7 +3722,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3683,13 +3731,13 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -3700,14 +3748,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3726,15 +3774,17 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3783,7 +3833,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3792,31 +3842,31 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3835,15 +3885,17 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3892,7 +3944,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3901,27 +3953,27 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3944,17 +3996,19 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="M22" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -4003,7 +4057,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4012,13 +4066,13 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
@@ -4029,14 +4083,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4055,16 +4109,16 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4114,7 +4168,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4123,31 +4177,31 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4166,16 +4220,16 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4225,7 +4279,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4234,27 +4288,27 @@
         <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4277,17 +4331,19 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4312,31 +4368,31 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4345,13 +4401,13 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4362,10 +4418,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4388,16 +4444,16 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4423,31 +4479,31 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Z26" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4456,16 +4512,16 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4473,10 +4529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4499,15 +4555,17 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4532,31 +4590,31 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4565,16 +4623,16 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>76</v>
@@ -4582,14 +4640,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4608,16 +4666,16 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4667,7 +4725,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4676,27 +4734,27 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4719,15 +4777,17 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -4776,7 +4836,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4785,27 +4845,27 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4828,13 +4888,13 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4885,7 +4945,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4894,27 +4954,27 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4937,13 +4997,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4994,7 +5054,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5003,27 +5063,27 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5046,15 +5106,17 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5103,7 +5165,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5112,27 +5174,27 @@
         <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5155,16 +5217,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5214,7 +5276,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5223,16 +5285,16 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5240,10 +5302,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5266,13 +5328,13 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5323,7 +5385,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5332,13 +5394,13 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5349,10 +5411,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5375,13 +5437,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5432,7 +5494,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5447,7 +5509,7 @@
         <v>76</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5458,14 +5520,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5484,16 +5546,16 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5531,19 +5593,19 @@
         <v>76</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5552,13 +5614,13 @@
         <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5569,14 +5631,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5595,19 +5657,19 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5656,7 +5718,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5665,13 +5727,13 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5682,14 +5744,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5708,15 +5770,17 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5765,7 +5829,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>84</v>
@@ -5774,13 +5838,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5791,10 +5855,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5817,15 +5881,17 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -5850,13 +5916,13 @@
         <v>76</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>76</v>
@@ -5874,7 +5940,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>84</v>
@@ -5883,16 +5949,16 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -5900,10 +5966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5926,15 +5992,17 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -5983,7 +6051,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5992,16 +6060,16 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -6009,10 +6077,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6035,16 +6103,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6094,7 +6162,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6103,16 +6171,16 @@
         <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6120,10 +6188,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6146,15 +6214,17 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6179,13 +6249,13 @@
         <v>76</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>76</v>
@@ -6203,7 +6273,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6212,13 +6282,13 @@
         <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
@@ -6229,10 +6299,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6255,13 +6325,13 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6312,7 +6382,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6321,13 +6391,13 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6338,10 +6408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6364,13 +6434,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6421,7 +6491,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6436,7 +6506,7 @@
         <v>76</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
@@ -6447,14 +6517,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6473,16 +6543,16 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6520,19 +6590,19 @@
         <v>76</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6541,13 +6611,13 @@
         <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
@@ -6558,14 +6628,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6584,19 +6654,19 @@
         <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6645,7 +6715,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6654,13 +6724,13 @@
         <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
@@ -6671,14 +6741,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6697,15 +6767,17 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6754,7 +6826,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>84</v>
@@ -6763,13 +6835,13 @@
         <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
@@ -6780,10 +6852,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6806,15 +6878,17 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -6863,7 +6937,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6872,16 +6946,16 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>76</v>
@@ -6889,10 +6963,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6915,13 +6989,13 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6972,7 +7046,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6981,13 +7055,13 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
@@ -6998,10 +7072,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7024,13 +7098,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7081,7 +7155,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7096,7 +7170,7 @@
         <v>76</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
@@ -7107,14 +7181,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7133,16 +7207,16 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7180,19 +7254,19 @@
         <v>76</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7201,13 +7275,13 @@
         <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
@@ -7218,14 +7292,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7244,19 +7318,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7305,7 +7379,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7314,13 +7388,13 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
@@ -7331,14 +7405,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7357,15 +7431,17 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7414,7 +7490,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7423,13 +7499,13 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
@@ -7440,10 +7516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7466,13 +7542,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7523,7 +7599,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7532,16 +7608,16 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>76</v>
@@ -7549,10 +7625,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7575,15 +7651,17 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7632,7 +7710,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -7641,13 +7719,13 @@
         <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7658,10 +7736,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7684,13 +7762,13 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7741,7 +7819,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7750,13 +7828,13 @@
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
@@ -7767,10 +7845,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7793,13 +7871,13 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7850,7 +7928,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7865,7 +7943,7 @@
         <v>76</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -7876,14 +7954,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7902,16 +7980,16 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7949,19 +8027,19 @@
         <v>76</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -7970,13 +8048,13 @@
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
@@ -7987,14 +8065,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8013,19 +8091,19 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8074,7 +8152,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8083,13 +8161,13 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
@@ -8100,10 +8178,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8126,15 +8204,17 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8183,7 +8263,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
@@ -8192,13 +8272,13 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8209,10 +8289,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8235,15 +8315,17 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>76</v>
@@ -8292,7 +8374,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8301,13 +8383,13 @@
         <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>354</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>76</v>
+        <v>355</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8318,10 +8400,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8344,15 +8426,17 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>76</v>
@@ -8401,7 +8485,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8410,13 +8494,13 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8427,10 +8511,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8453,17 +8537,19 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -8512,7 +8598,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8521,16 +8607,16 @@
         <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>76</v>
@@ -8538,10 +8624,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8564,15 +8650,17 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8621,7 +8709,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8630,16 +8718,16 @@
         <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>76</v>
@@ -8647,10 +8735,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8673,16 +8761,16 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8732,7 +8820,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8741,16 +8829,16 @@
         <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>96</v>
+        <v>377</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>76</v>
@@ -8758,10 +8846,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8784,17 +8872,19 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -8843,7 +8933,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -8852,16 +8942,16 @@
         <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>76</v>
@@ -8869,10 +8959,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8895,16 +8985,16 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8954,7 +9044,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -8963,16 +9053,16 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>76</v>
@@ -8980,10 +9070,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9006,15 +9096,17 @@
         <v>76</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9063,7 +9155,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9072,13 +9164,13 @@
         <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
@@ -9089,10 +9181,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9115,15 +9207,17 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>76</v>
@@ -9172,7 +9266,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9181,13 +9275,13 @@
         <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>76</v>
@@ -9198,10 +9292,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9224,15 +9318,17 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9281,7 +9377,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9290,13 +9386,13 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>76</v>

--- a/main/ig/StructureDefinition-dmi-device.xlsx
+++ b/main/ig/StructureDefinition-dmi-device.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="391">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Device.id</t>
@@ -307,204 +307,195 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Device.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Device.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Device.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Device.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Device.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Device.extension:IPIdLogiciel</t>
+  </si>
+  <si>
+    <t>IPIdLogiciel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-ip-id-logiciel}
+</t>
+  </si>
+  <si>
+    <t>DMI IP Id logiciel</t>
+  </si>
+  <si>
+    <t>Extension créée dans ce volet pour représenter l'IP Id logiciel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>Device.extension:MarquageCE</t>
+  </si>
+  <si>
+    <t>MarquageCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-marquage-ce}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Device.implicitRules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
+    <t>DMI Marquage CE</t>
+  </si>
+  <si>
+    <t>Extension créée dans ce volet pour représenter le marquage CE.</t>
+  </si>
+  <si>
+    <t>Device.extension:CodeEMDN</t>
+  </si>
+  <si>
+    <t>CodeEMDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-code-emdn}
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Device.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Device.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Device.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>Device.extension</t>
+    <t>DMI Code EMDN</t>
+  </si>
+  <si>
+    <t>Extension créée dans ce volet pour représenter le code EMDN.</t>
+  </si>
+  <si>
+    <t>Device.modifierExtension</t>
   </si>
   <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Device.extension:IPIdLogiciel</t>
-  </si>
-  <si>
-    <t>IPIdLogiciel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-ip-id-logiciel}
-</t>
-  </si>
-  <si>
-    <t>DMI IP Id logiciel</t>
-  </si>
-  <si>
-    <t>Extension créée dans ce volet pour représenter l'IP Id logiciel.</t>
-  </si>
-  <si>
-    <t>Device.extension:MarquageCE</t>
-  </si>
-  <si>
-    <t>MarquageCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-marquage-ce}
-</t>
-  </si>
-  <si>
-    <t>DMI Marquage CE</t>
-  </si>
-  <si>
-    <t>Extension créée dans ce volet pour représenter le marquage CE.</t>
-  </si>
-  <si>
-    <t>Device.extension:CodeEMDN</t>
-  </si>
-  <si>
-    <t>CodeEMDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-code-emdn}
-</t>
-  </si>
-  <si>
-    <t>DMI Code EMDN</t>
-  </si>
-  <si>
-    <t>Extension créée dans ce volet pour représenter le code EMDN.</t>
-  </si>
-  <si>
-    <t>Device.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -512,6 +503,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -556,16 +550,6 @@
     <t>The reference to the definition for the device.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
     <t>Device.udiCarrier</t>
   </si>
   <si>
@@ -601,7 +585,13 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Device.udiCarrier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -638,9 +628,6 @@
   </si>
   <si>
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Role.id.extension</t>
@@ -673,9 +660,6 @@
 http://hl7.org/fhir/NamingSystem/iccbba-other-di.</t>
   </si>
   <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
-  </si>
-  <si>
     <t>Role.id.root</t>
   </si>
   <si>
@@ -808,9 +792,6 @@
     <t>Reason for the dtatus of the Device availability.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -818,9 +799,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>CD</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -1076,9 +1054,6 @@
     <t>A single component of the device version.</t>
   </si>
   <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
     <t>Device.version.value</t>
   </si>
   <si>
@@ -1128,16 +1103,6 @@
     <t>Property value as a quantity.</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
     <t>Device.property.valueCode</t>
   </si>
   <si>
@@ -1204,10 +1169,6 @@
     <t>used for troubleshooting etc.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
-  </si>
-  <si>
     <t>.scopedRole[typeCode=CON].player</t>
   </si>
   <si>
@@ -1259,9 +1220,6 @@
   </si>
   <si>
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>.text</t>
@@ -1619,14 +1577,14 @@
     <col min="26" max="26" width="43.49609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="52.640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="230.36328125" customWidth="true" bestFit="true"/>
   </cols>
@@ -2064,13 +2022,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>76</v>
@@ -2081,10 +2039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2107,16 +2065,16 @@
         <v>85</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2166,7 +2124,7 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
@@ -2175,13 +2133,13 @@
         <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK5" t="s" s="2">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>76</v>
@@ -2192,10 +2150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2218,16 +2176,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2253,31 +2211,31 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -2286,13 +2244,13 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK6" t="s" s="2">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>76</v>
@@ -2303,14 +2261,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2329,16 +2287,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2388,7 +2346,7 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
@@ -2397,13 +2355,13 @@
         <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK7" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>76</v>
@@ -2414,14 +2372,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2440,16 +2398,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2499,7 +2457,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2514,7 +2472,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>76</v>
@@ -2525,14 +2483,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2551,17 +2509,15 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>76</v>
@@ -2598,19 +2554,17 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2619,13 +2573,13 @@
         <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>76</v>
@@ -2636,13 +2590,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -2664,13 +2618,13 @@
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2721,7 +2675,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2730,10 +2684,10 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2747,13 +2701,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>76</v>
@@ -2775,13 +2729,13 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2832,7 +2786,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2841,10 +2795,10 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>76</v>
@@ -2858,13 +2812,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>76</v>
@@ -2886,13 +2840,13 @@
         <v>76</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2943,7 +2897,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2952,10 +2906,10 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>76</v>
@@ -2969,14 +2923,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2995,19 +2949,19 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O13" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -3044,19 +2998,19 @@
         <v>76</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3065,13 +3019,13 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
@@ -3082,10 +3036,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3108,16 +3062,16 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3167,7 +3121,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3176,27 +3130,27 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3219,17 +3173,15 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3278,7 +3230,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3287,13 +3239,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>174</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -3304,10 +3256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3330,16 +3282,16 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3389,7 +3341,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3398,16 +3350,16 @@
         <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>76</v>
@@ -3415,10 +3367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3441,13 +3393,13 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3498,7 +3450,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3513,7 +3465,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3524,14 +3476,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3550,16 +3502,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3597,19 +3549,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3618,13 +3570,13 @@
         <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3635,14 +3587,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3661,19 +3613,19 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3722,7 +3674,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3731,13 +3683,13 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -3748,14 +3700,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3774,17 +3726,15 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3833,7 +3783,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3842,31 +3792,31 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ20" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK20" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3885,17 +3835,15 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3944,7 +3892,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3953,27 +3901,27 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ21" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK21" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3996,19 +3944,17 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N22" t="s" s="2">
         <v>207</v>
       </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -4057,7 +4003,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4066,13 +4012,13 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK22" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
@@ -4083,14 +4029,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4109,16 +4055,16 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4168,7 +4114,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4177,31 +4123,31 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ23" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK23" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4220,16 +4166,16 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4279,7 +4225,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4288,27 +4234,27 @@
         <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK24" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4331,19 +4277,17 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4368,13 +4312,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4392,7 +4336,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4401,13 +4345,13 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK25" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4418,10 +4362,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4444,16 +4388,16 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4479,13 +4423,13 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -4503,7 +4447,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4512,16 +4456,16 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK26" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4529,10 +4473,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4555,17 +4499,15 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4590,13 +4532,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4614,7 +4556,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4623,16 +4565,16 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK27" t="s" s="2">
-        <v>252</v>
+        <v>76</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>76</v>
@@ -4640,14 +4582,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4666,16 +4608,16 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4725,7 +4667,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4734,27 +4676,27 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK28" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4777,17 +4719,15 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -4836,7 +4776,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4845,27 +4785,27 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK29" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>98</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4888,13 +4828,13 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4945,7 +4885,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4954,27 +4894,27 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK30" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4997,13 +4937,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5054,7 +4994,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5063,27 +5003,27 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ31" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK31" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5106,17 +5046,15 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5165,7 +5103,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5174,27 +5112,27 @@
         <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ32" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK32" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5217,16 +5155,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5276,7 +5214,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5285,16 +5223,16 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK33" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5302,10 +5240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5328,13 +5266,13 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5385,7 +5323,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5394,13 +5332,13 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK34" t="s" s="2">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5411,10 +5349,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5437,13 +5375,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5494,7 +5432,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5509,7 +5447,7 @@
         <v>76</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5520,14 +5458,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5546,16 +5484,16 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5593,19 +5531,19 @@
         <v>76</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5614,13 +5552,13 @@
         <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5631,14 +5569,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5657,19 +5595,19 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5718,7 +5656,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5727,13 +5665,13 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5744,14 +5682,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5770,17 +5708,15 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5829,7 +5765,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>84</v>
@@ -5838,13 +5774,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK38" t="s" s="2">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5855,10 +5791,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5881,17 +5817,15 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -5916,13 +5850,13 @@
         <v>76</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>76</v>
@@ -5940,7 +5874,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>84</v>
@@ -5949,16 +5883,16 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK39" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -5966,10 +5900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5992,17 +5926,15 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -6051,7 +5983,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6060,16 +5992,16 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ40" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK40" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -6077,10 +6009,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6103,16 +6035,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6162,7 +6094,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6171,16 +6103,16 @@
         <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK41" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6188,10 +6120,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6214,17 +6146,15 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6249,13 +6179,13 @@
         <v>76</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>76</v>
@@ -6273,7 +6203,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6282,13 +6212,13 @@
         <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ42" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK42" t="s" s="2">
-        <v>252</v>
+        <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
@@ -6299,10 +6229,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6325,13 +6255,13 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6382,7 +6312,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6391,13 +6321,13 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ43" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK43" t="s" s="2">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6408,10 +6338,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6434,13 +6364,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6491,7 +6421,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6506,7 +6436,7 @@
         <v>76</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
@@ -6517,14 +6447,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6543,16 +6473,16 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6590,19 +6520,19 @@
         <v>76</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6611,13 +6541,13 @@
         <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
@@ -6628,14 +6558,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6654,19 +6584,19 @@
         <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6715,7 +6645,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6724,13 +6654,13 @@
         <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
@@ -6741,14 +6671,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6767,17 +6697,15 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6826,7 +6754,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>84</v>
@@ -6835,13 +6763,13 @@
         <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK47" t="s" s="2">
-        <v>252</v>
+        <v>76</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
@@ -6852,10 +6780,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6878,17 +6806,15 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -6937,7 +6863,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6946,16 +6872,16 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK48" t="s" s="2">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>76</v>
@@ -6963,10 +6889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6989,13 +6915,13 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7046,7 +6972,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7055,13 +6981,13 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK49" t="s" s="2">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
@@ -7072,10 +6998,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7098,13 +7024,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7155,7 +7081,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7170,7 +7096,7 @@
         <v>76</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
@@ -7181,14 +7107,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7207,16 +7133,16 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7254,19 +7180,19 @@
         <v>76</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7275,13 +7201,13 @@
         <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
@@ -7292,14 +7218,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7318,19 +7244,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7379,7 +7305,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7388,13 +7314,13 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
@@ -7405,14 +7331,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7431,17 +7357,15 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7490,7 +7414,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7499,13 +7423,13 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ53" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK53" t="s" s="2">
-        <v>252</v>
+        <v>76</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
@@ -7516,10 +7440,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7542,13 +7466,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7599,7 +7523,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7608,16 +7532,16 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK54" t="s" s="2">
-        <v>336</v>
+        <v>76</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>76</v>
@@ -7625,10 +7549,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7651,17 +7575,15 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7710,7 +7632,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -7719,13 +7641,13 @@
         <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ55" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK55" t="s" s="2">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7736,10 +7658,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7762,13 +7684,13 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7819,7 +7741,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7828,13 +7750,13 @@
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ56" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK56" t="s" s="2">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
@@ -7845,10 +7767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7871,13 +7793,13 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7928,7 +7850,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7943,7 +7865,7 @@
         <v>76</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -7954,14 +7876,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7980,16 +7902,16 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8027,19 +7949,19 @@
         <v>76</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8048,13 +7970,13 @@
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
@@ -8065,14 +7987,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8091,19 +8013,19 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8152,7 +8074,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8161,13 +8083,13 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
@@ -8178,10 +8100,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8204,17 +8126,15 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8263,7 +8183,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
@@ -8272,13 +8192,13 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK60" t="s" s="2">
-        <v>252</v>
+        <v>76</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8289,10 +8209,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8315,17 +8235,15 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>76</v>
@@ -8374,7 +8292,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8383,13 +8301,13 @@
         <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>354</v>
-      </c>
       <c r="AK61" t="s" s="2">
-        <v>355</v>
+        <v>76</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8400,10 +8318,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8426,17 +8344,15 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>76</v>
@@ -8485,7 +8401,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8494,13 +8410,13 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ62" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK62" t="s" s="2">
-        <v>252</v>
+        <v>76</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8511,10 +8427,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8537,19 +8453,17 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -8598,7 +8512,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8607,16 +8521,16 @@
         <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ63" t="s" s="2">
-        <v>174</v>
-      </c>
       <c r="AK63" t="s" s="2">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>76</v>
@@ -8624,10 +8538,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8650,17 +8564,15 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8709,7 +8621,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8718,16 +8630,16 @@
         <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ64" t="s" s="2">
-        <v>174</v>
-      </c>
       <c r="AK64" t="s" s="2">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>76</v>
@@ -8735,10 +8647,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8761,16 +8673,16 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8820,7 +8732,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8829,16 +8741,16 @@
         <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ65" t="s" s="2">
-        <v>377</v>
-      </c>
       <c r="AK65" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>76</v>
@@ -8846,10 +8758,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8872,19 +8784,17 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -8933,7 +8843,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -8942,16 +8852,16 @@
         <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ66" t="s" s="2">
-        <v>174</v>
-      </c>
       <c r="AK66" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>76</v>
@@ -8959,10 +8869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8985,16 +8895,16 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9044,7 +8954,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9053,16 +8963,16 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK67" t="s" s="2">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>76</v>
@@ -9070,10 +8980,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9096,17 +9006,15 @@
         <v>76</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9155,7 +9063,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9164,13 +9072,13 @@
         <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK68" t="s" s="2">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
@@ -9181,10 +9089,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9207,17 +9115,15 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>76</v>
@@ -9266,7 +9172,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9275,13 +9181,13 @@
         <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK69" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>76</v>
@@ -9292,10 +9198,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9318,17 +9224,15 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9377,7 +9281,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9386,13 +9290,13 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>174</v>
-      </c>
       <c r="AK70" t="s" s="2">
-        <v>175</v>
+        <v>76</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>76</v>

--- a/main/ig/StructureDefinition-dmi-device.xlsx
+++ b/main/ig/StructureDefinition-dmi-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-device.xlsx
+++ b/main/ig/StructureDefinition-dmi-device.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="404">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Device.id</t>
@@ -307,10 +307,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Device.implicitRules</t>
   </si>
   <si>
@@ -330,6 +337,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Device.language</t>
   </si>
   <si>
@@ -407,26 +417,33 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Device.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -453,10 +470,6 @@
     <t>Extension créée dans ce volet pour représenter l'IP Id logiciel.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Device.extension:MarquageCE</t>
   </si>
   <si>
@@ -492,10 +505,6 @@
     <t>Device.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -503,9 +512,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -550,6 +556,16 @@
     <t>The reference to the definition for the device.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>Device.udiCarrier</t>
   </si>
   <si>
@@ -585,13 +601,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Device.udiCarrier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -628,6 +638,9 @@
   </si>
   <si>
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Role.id.extension</t>
@@ -660,6 +673,9 @@
 http://hl7.org/fhir/NamingSystem/iccbba-other-di.</t>
   </si>
   <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
+  </si>
+  <si>
     <t>Role.id.root</t>
   </si>
   <si>
@@ -792,6 +808,9 @@
     <t>Reason for the dtatus of the Device availability.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -799,6 +818,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>CD</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -1054,6 +1076,9 @@
     <t>A single component of the device version.</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Device.version.value</t>
   </si>
   <si>
@@ -1103,6 +1128,16 @@
     <t>Property value as a quantity.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+  </si>
+  <si>
     <t>Device.property.valueCode</t>
   </si>
   <si>
@@ -1169,6 +1204,10 @@
     <t>used for troubleshooting etc.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
+  </si>
+  <si>
     <t>.scopedRole[typeCode=CON].player</t>
   </si>
   <si>
@@ -1220,6 +1259,9 @@
   </si>
   <si>
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>.text</t>
@@ -1577,14 +1619,14 @@
     <col min="26" max="26" width="43.49609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="52.640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="230.36328125" customWidth="true" bestFit="true"/>
   </cols>
@@ -2022,13 +2064,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>76</v>
@@ -2039,10 +2081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2065,16 +2107,16 @@
         <v>85</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2124,7 +2166,7 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
@@ -2133,13 +2175,13 @@
         <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>76</v>
@@ -2150,10 +2192,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2176,16 +2218,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2211,13 +2253,13 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -2235,7 +2277,7 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -2244,13 +2286,13 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>76</v>
@@ -2261,14 +2303,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2287,16 +2329,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2346,7 +2388,7 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
@@ -2355,13 +2397,13 @@
         <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>76</v>
@@ -2372,14 +2414,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2398,16 +2440,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2457,7 +2499,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2472,7 +2514,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>76</v>
@@ -2483,14 +2525,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2509,15 +2551,17 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>76</v>
@@ -2554,17 +2598,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2573,13 +2619,13 @@
         <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>76</v>
@@ -2590,13 +2636,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -2618,13 +2664,13 @@
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2675,7 +2721,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2684,10 +2730,10 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2701,13 +2747,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>76</v>
@@ -2729,13 +2775,13 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2786,7 +2832,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2795,10 +2841,10 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>76</v>
@@ -2812,13 +2858,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>76</v>
@@ -2840,13 +2886,13 @@
         <v>76</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2897,7 +2943,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2906,10 +2952,10 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>76</v>
@@ -2923,14 +2969,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2949,19 +2995,19 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -2998,19 +3044,19 @@
         <v>76</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3019,13 +3065,13 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
@@ -3036,10 +3082,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3062,16 +3108,16 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3121,7 +3167,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3130,27 +3176,27 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3173,15 +3219,17 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3230,7 +3278,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3239,13 +3287,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -3256,10 +3304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3282,16 +3330,16 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3341,7 +3389,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3350,16 +3398,16 @@
         <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>76</v>
@@ -3367,10 +3415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3393,13 +3441,13 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3450,7 +3498,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3465,7 +3513,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3476,14 +3524,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3502,16 +3550,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3549,19 +3597,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3570,13 +3618,13 @@
         <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3587,14 +3635,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3613,19 +3661,19 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3674,7 +3722,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3683,13 +3731,13 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -3700,14 +3748,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3726,15 +3774,17 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3783,7 +3833,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3792,31 +3842,31 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3835,15 +3885,17 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3892,7 +3944,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3901,27 +3953,27 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3944,17 +3996,19 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="M22" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -4003,7 +4057,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4012,13 +4066,13 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
@@ -4029,14 +4083,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4055,16 +4109,16 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4114,7 +4168,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4123,31 +4177,31 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4166,16 +4220,16 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4225,7 +4279,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4234,27 +4288,27 @@
         <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4277,17 +4331,19 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4312,31 +4368,31 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4345,13 +4401,13 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4362,10 +4418,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4388,16 +4444,16 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4423,31 +4479,31 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Z26" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4456,16 +4512,16 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4473,10 +4529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4499,15 +4555,17 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4532,31 +4590,31 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4565,16 +4623,16 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>76</v>
@@ -4582,14 +4640,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4608,16 +4666,16 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4667,7 +4725,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4676,27 +4734,27 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4719,15 +4777,17 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -4776,7 +4836,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4785,27 +4845,27 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4828,13 +4888,13 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4885,7 +4945,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4894,27 +4954,27 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4937,13 +4997,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4994,7 +5054,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5003,27 +5063,27 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5046,15 +5106,17 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5103,7 +5165,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5112,27 +5174,27 @@
         <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5155,16 +5217,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5214,7 +5276,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5223,16 +5285,16 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5240,10 +5302,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5266,13 +5328,13 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5323,7 +5385,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5332,13 +5394,13 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5349,10 +5411,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5375,13 +5437,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5432,7 +5494,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5447,7 +5509,7 @@
         <v>76</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5458,14 +5520,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5484,16 +5546,16 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5531,19 +5593,19 @@
         <v>76</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5552,13 +5614,13 @@
         <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5569,14 +5631,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5595,19 +5657,19 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5656,7 +5718,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5665,13 +5727,13 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5682,14 +5744,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5708,15 +5770,17 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5765,7 +5829,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>84</v>
@@ -5774,13 +5838,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5791,10 +5855,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5817,15 +5881,17 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -5850,13 +5916,13 @@
         <v>76</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>76</v>
@@ -5874,7 +5940,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>84</v>
@@ -5883,16 +5949,16 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -5900,10 +5966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5926,15 +5992,17 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -5983,7 +6051,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5992,16 +6060,16 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -6009,10 +6077,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6035,16 +6103,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6094,7 +6162,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6103,16 +6171,16 @@
         <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6120,10 +6188,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6146,15 +6214,17 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6179,13 +6249,13 @@
         <v>76</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>76</v>
@@ -6203,7 +6273,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6212,13 +6282,13 @@
         <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
@@ -6229,10 +6299,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6255,13 +6325,13 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6312,7 +6382,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6321,13 +6391,13 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6338,10 +6408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6364,13 +6434,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6421,7 +6491,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6436,7 +6506,7 @@
         <v>76</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
@@ -6447,14 +6517,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6473,16 +6543,16 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6520,19 +6590,19 @@
         <v>76</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6541,13 +6611,13 @@
         <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
@@ -6558,14 +6628,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6584,19 +6654,19 @@
         <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6645,7 +6715,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6654,13 +6724,13 @@
         <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
@@ -6671,14 +6741,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6697,15 +6767,17 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6754,7 +6826,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>84</v>
@@ -6763,13 +6835,13 @@
         <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
@@ -6780,10 +6852,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6806,15 +6878,17 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -6863,7 +6937,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6872,16 +6946,16 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>76</v>
@@ -6889,10 +6963,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6915,13 +6989,13 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6972,7 +7046,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6981,13 +7055,13 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
@@ -6998,10 +7072,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7024,13 +7098,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7081,7 +7155,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7096,7 +7170,7 @@
         <v>76</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
@@ -7107,14 +7181,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7133,16 +7207,16 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7180,19 +7254,19 @@
         <v>76</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7201,13 +7275,13 @@
         <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
@@ -7218,14 +7292,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7244,19 +7318,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7305,7 +7379,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7314,13 +7388,13 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
@@ -7331,14 +7405,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7357,15 +7431,17 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7414,7 +7490,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7423,13 +7499,13 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
@@ -7440,10 +7516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7466,13 +7542,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7523,7 +7599,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7532,16 +7608,16 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>76</v>
@@ -7549,10 +7625,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7575,15 +7651,17 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7632,7 +7710,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -7641,13 +7719,13 @@
         <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7658,10 +7736,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7684,13 +7762,13 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7741,7 +7819,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7750,13 +7828,13 @@
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
@@ -7767,10 +7845,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7793,13 +7871,13 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7850,7 +7928,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7865,7 +7943,7 @@
         <v>76</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -7876,14 +7954,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7902,16 +7980,16 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7949,19 +8027,19 @@
         <v>76</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -7970,13 +8048,13 @@
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
@@ -7987,14 +8065,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8013,19 +8091,19 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8074,7 +8152,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8083,13 +8161,13 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
@@ -8100,10 +8178,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8126,15 +8204,17 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8183,7 +8263,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
@@ -8192,13 +8272,13 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8209,10 +8289,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8235,15 +8315,17 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>76</v>
@@ -8292,7 +8374,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8301,13 +8383,13 @@
         <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>354</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>76</v>
+        <v>355</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8318,10 +8400,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8344,15 +8426,17 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>76</v>
@@ -8401,7 +8485,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8410,13 +8494,13 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8427,10 +8511,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8453,17 +8537,19 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -8512,7 +8598,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8521,16 +8607,16 @@
         <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>76</v>
@@ -8538,10 +8624,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8564,15 +8650,17 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8621,7 +8709,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8630,16 +8718,16 @@
         <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>76</v>
@@ -8647,10 +8735,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8673,16 +8761,16 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8732,7 +8820,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8741,16 +8829,16 @@
         <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>96</v>
+        <v>377</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>76</v>
@@ -8758,10 +8846,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8784,17 +8872,19 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -8843,7 +8933,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -8852,16 +8942,16 @@
         <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>76</v>
@@ -8869,10 +8959,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8895,16 +8985,16 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8954,7 +9044,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -8963,16 +9053,16 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>76</v>
@@ -8980,10 +9070,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9006,15 +9096,17 @@
         <v>76</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9063,7 +9155,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9072,13 +9164,13 @@
         <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
@@ -9089,10 +9181,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9115,15 +9207,17 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>76</v>
@@ -9172,7 +9266,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9181,13 +9275,13 @@
         <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>76</v>
@@ -9198,10 +9292,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9224,15 +9318,17 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9281,7 +9377,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9290,13 +9386,13 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>76</v>
